--- a/labels/labels_review.xlsx
+++ b/labels/labels_review.xlsx
@@ -10740,7 +10740,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>A light blue painted field inside a rough white border, with a horizontal row of small colored dots in pink, green, orange, blue and red. Thin black and grey pencil-like lines and scribbles run around and through the dots. The work is behind glass with visible reflections.</t>
+          <t>A light blue painted field inside a rough white border, with a horizontal row of small colored dots in pink, green, orange, blue and red. Thin black and grey pencil-like lines and scribbles run around and through the dots.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>mixed media on paper, under glass (guess)</t>
+          <t>mixed media on paper (guess)</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>flat, with glare reflections on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>A misty landscape with a single blue tree in the center, standing above a field of grey, rocky texture. The upper part is filled with soft white cloud and grey haze. A signature reading 'Vanni' appears in the lower left; the work is matted and framed behind glass.</t>
+          <t>A misty landscape with a single blue tree in the center, standing above a field of grey, rocky texture. The upper part is filled with soft white cloud and grey haze.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -10940,7 +10940,7 @@
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>An abstract work with vertical streaks and scraped layers of red, pink, ochre, gold and white over a pale blue ground. The surface looks scraped and dripped, revealing underlayers. Strong reflections of a window and room are visible on the glass.</t>
+          <t>An abstract work with vertical streaks and scraped layers of red, pink, ochre, gold and white over a pale blue ground. The surface looks scraped and dripped, revealing underlayers.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>flat, with strong glare reflections on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -11436,7 +11436,7 @@
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>A collage-like composition of elegant figures in long coats, hats and gowns arranged across red, blue, grey and white color blocks. Handwritten text fragments, a red plant and a blue X shape appear among the figures. The work is framed behind glass with visible reflections.</t>
+          <t>A collage-like composition of elegant figures in long coats, hats and gowns arranged across red, blue, grey and white color blocks. Handwritten text fragments, a red plant and a blue X shape appear among the figures.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>flat, with reflections on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Same artwork as F1-016, photographed again: elegant figures in coats, hats and gowns over red, blue, grey and white color blocks, with handwritten text fragments, a red plant and a blue X. Reflections on the glass are visible in the lower center.</t>
+          <t>Elegant figures in coats, hats and gowns over red, blue, grey and white color blocks, with handwritten text fragments, a red plant and a blue X.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>flat, with reflections on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -11836,7 +11836,7 @@
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>A densely detailed fantasy scene on a black background, filled with floating figures, masks, flowers, swirling ornaments and patterned shapes. A white round object sits near the center and a jester-like figure appears in the lower right. Initials and '24' are written in the lower left; the work is in a gold frame behind glass.</t>
+          <t>A densely detailed fantasy scene on a black background, filled with floating figures, masks, flowers, swirling ornaments and patterned shapes. A white round object sits near the center and a jester-like figure appears in the lower right.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>A vineyard landscape with rows of dark vine stems on bright green rolling slopes in the foreground. A large flat-topped khaki and brown mountain rises behind, under a pale olive sky. A signature is visible in the lower right.</t>
+          <t>A vineyard landscape with rows of dark vine stems on bright green rolling slopes in the foreground. A large flat-topped khaki and brown mountain rises behind, under a pale olive sky.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -12552,7 +12552,7 @@
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>A small angel in a long blue robe with white wings and golden hair is painted on a dark bird feather, mounted on a white board. The angel holds a golden panpipe-like instrument and stands on grey rocks. 'Puerto Rico' is written in the upper left and a signature with '2023' in the lower right.</t>
+          <t>A small angel in a long blue robe with white wings and golden hair is painted on a dark bird feather, mounted on a white board. The angel holds a golden panpipe-like instrument and stands on grey rocks. 'Puerto Rico' is written in the upper left.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>flat, with shadow of photographer on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>A grey smoky field with soot-like dark patches and layered translucent paper shapes. Thin red curving lines loop across the surface like a maze. A small signature appears in the lower right.</t>
+          <t>A grey smoky field with soot-like dark patches and layered translucent paper shapes. Thin red curving lines loop across the surface like a maze.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Two stylized female faces with long multicolored streaked hair, red cheeks and red lips lean toward each other on a grey-green background. They are drawn in pastel-like lines in blue, pink, green and white. A signature 'Tekla Mela...' is in the lower right; the photographer is reflected in the glass.</t>
+          <t>Two stylized female faces with long multicolored streaked hair, red cheeks and red lips lean toward each other on a grey-green background. They are drawn in pastel-like lines in blue, pink, green and white.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>flat, with reflections on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A still life of a dark green bottle and a large olive-colored two-handled jug, with three red pomegranates in front on a crumpled white cloth. A pale green and pink drapery hangs behind. There are reflections on the glass.</t>
+          <t>A still life of a dark green bottle and a large olive-colored two-handled jug, with three red pomegranates in front on a crumpled white cloth. A pale green and pink drapery hangs behind.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Same artwork as F1-040, photographed again: a dark green bottle and an olive two-handled jug with three red pomegranates on a crumpled white cloth, against green and pink drapery. Reflections on the glass are visible.</t>
+          <t>A dark green bottle and an olive two-handled jug with three red pomegranates on a crumpled white cloth, against green and pink drapery.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -13728,7 +13728,7 @@
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Three blue-violet irises with yellow beards and green stems stand against a golden ochre background. Thick impasto gives the petals a sculpted texture. Initials 'A.T.' and '2016' are written in the lower right.</t>
+          <t>Three blue-violet irises with yellow beards and green stems stand against a golden ochre background. Thick impasto gives the petals a sculpted texture.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -13828,7 +13828,7 @@
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>A woven or embroidered tapestry-like image of a bright interior with white curtains and a vase of pink and dark flowers in the lower left. Soft lilac, cream and grey tones dominate, and the stitched texture is visible. Reflections of ceiling lights appear on the glass.</t>
+          <t>A woven or embroidered tapestry-like image of a bright interior with white curtains and a vase of pink and dark flowers in the lower left. Soft lilac, cream and grey tones dominate, and the stitched texture is visible.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -13928,7 +13928,7 @@
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>A tapestry-like landscape of a village with small white and pink houses among purple, orange and red flowering trees. Green and lilac hills rise behind under a blue and white sky. The stitched texture is visible, with light reflections on the glass.</t>
+          <t>A tapestry-like landscape of a village with small white and pink houses among purple, orange and red flowering trees. Green and lilac hills rise behind under a blue and white sky. The stitched texture is visible.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -14028,7 +14028,7 @@
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>A stylized female figure with a faceless pale oval head and flowing auburn hair, wearing a long rust-red dress that sweeps diagonally across the canvas. The background is cream and ochre with soft brown shadows. A signature 'B' with '2010' appears in the lower right.</t>
+          <t>A stylized female figure with a faceless pale oval head and flowing auburn hair, wearing a long rust-red dress that sweeps diagonally across the canvas. The background is cream and ochre with soft brown shadows.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -14128,7 +14128,7 @@
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>A field of red, orange and yellow flowers under a blue sky, covered with dense splatters and drips of white, yellow and orange paint. Green stems fill the lower part. The work is behind glass with a window reflection.</t>
+          <t>A field of red, orange and yellow flowers under a blue sky, covered with dense splatters and drips of white, yellow and orange paint. Green stems fill the lower part.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>bright, flat, with reflections on glass</t>
+          <t>bright, flat</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -14328,7 +14328,7 @@
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>A lively ballroom or festive scene with women in long red, pink and white gowns dancing beneath hanging garlands and streamers. The strokes are loose and expressive in yellow, pink, green and white. A signature appears in the lower left; the work is matted behind glass.</t>
+          <t>A lively ballroom or festive scene with women in long red, pink and white gowns dancing beneath hanging garlands and streamers. The strokes are loose and expressive in yellow, pink, green and white.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>A calligraphic artwork in which black Arabic script forms the shape of a whirling dervish with a tall hat and flared skirt. Small red ornamented shapes mark the hat, a foot and a decorative medallion on the left. The ground is pale marbled cream, matted inside a dark frame.</t>
+          <t>A calligraphic artwork in which black Arabic script forms the shape of a whirling dervish with a tall hat and flared skirt. Small red ornamented shapes mark the hat, a foot and a decorative medallion on the left. The ground is pale marbled cream.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -14636,7 +14636,7 @@
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>A nude female figure with arms raised above her head appears to rise out of a large red hibiscus flower on the left. The canvas is filled with oversized red and orange hibiscus blossoms, opening onto a glowing yellow and turquoise space in the center. A signature is in the lower right.</t>
+          <t>A nude female figure with arms raised above her head appears to rise out of a large red hibiscus flower on the left. The canvas is filled with oversized red and orange hibiscus blossoms, opening onto a glowing yellow and turquoise space in the center.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -14736,7 +14736,7 @@
       <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Same artwork as F1-056, photographed again: a pale ribbed surreal figure in profile with a hammer in its head and a red anatomical heart outside the body inside a white geometric outline, on a dark green background with black branches.</t>
+          <t>A pale ribbed surreal figure in profile with a hammer in its head and a red anatomical heart outside the body inside a white geometric outline, on a dark green background with black branches.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>A dark still life with a crystal wine glass, a dark vase holding a branch of tiny white flowers, and two golden-yellow fruits on a table. Small colorful flower dots and white sparkles are scattered over the dark background like confetti or stars. A signature is in the lower right.</t>
+          <t>A dark still life with a crystal wine glass, a dark vase holding a branch of tiny white flowers, and two golden-yellow fruits on a table. Small colorful flower dots and white sparkles are scattered over the dark background like confetti or stars.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>A ballerina in a dramatic forward bend, with her dark hair in a bun and her legs extended in a bent pose. She is painted in white and grey against dark blue-grey vertical drips. A signature 'Bacho' appears in the lower right.</t>
+          <t>A ballerina in a dramatic forward bend, with her dark hair in a bun and her legs extended in a bent pose. She is painted in white and grey against dark blue-grey vertical drips.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>A loose, washed cityscape with grey-blue building facades on the right and pink and brown horizontal bands suggesting rooftops and sky. Grey clouds sit in a pale sky. White columns and dripping strokes are visible, with a signature in the lower right.</t>
+          <t>A loose, washed cityscape with grey-blue building facades on the right and pink and brown horizontal bands suggesting rooftops and sky. Grey clouds sit in a pale sky. White columns and dripping strokes are visible.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -15484,7 +15484,7 @@
       <c r="F56" s="2" t="n"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>A long horizontal drawing of a hilly landscape with scattered houses, small trees, a few pink blossoming trees and grazing animals. Blue mountains run along the top. It is drawn with charcoal and colored crayon on cream paper and signed in the lower right.</t>
+          <t>A long horizontal drawing of a hilly landscape with scattered houses, small trees, a few pink blossoming trees and grazing animals. Blue mountains run along the top. It is drawn with charcoal and colored crayon on cream paper.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -15580,7 +15580,7 @@
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>A soft pastel landscape of rounded hills in ochre, pink, grey and violet patches. A single red tree with a black trunk stands in the lower right. A signature is in the lower right corner.</t>
+          <t>A soft pastel landscape of rounded hills in ochre, pink, grey and violet patches. A single red tree with a black trunk stands in the lower right.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -15680,7 +15680,7 @@
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>A simple pastel landscape with three green trees with black trunks on an ochre ground. Behind them are blue hills, and a single black bird flies in a pale grey sky. A signature is in the lower right.</t>
+          <t>A simple pastel landscape with three green trees with black trunks on an ochre ground. Behind them are blue hills, and a single black bird flies in a pale grey sky.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -15780,7 +15780,7 @@
       <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>A vase of flowers on a brown background: red poppies with black centers and white daisies with yellow centers above a dark, squat black vase. Green leaves are dabbed between the flowers. A signature is in the lower right.</t>
+          <t>A vase of flowers on a brown background: red poppies with black centers and white daisies with yellow centers above a dark, squat black vase. Green leaves are dabbed between the flowers.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -15880,7 +15880,7 @@
       <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>A landscape with a pale ochre hill and a stone tower or fortress on top, with dark blue and pink shapes suggesting trees or buildings. Strong reflections of the photographer and the room on the glass obscure most of the lower half.</t>
+          <t>A landscape with a pale ochre hill and a stone tower or fortress on top, with dark blue and pink shapes suggesting trees or buildings.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>obscured by glass reflections</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -16716,7 +16716,7 @@
       <c r="F68" s="2" t="n"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Pale pink four-petaled blossoms with yellow centers drift across a deep blue-violet background with pink and turquoise bands near the top. Thin white curved lines trail behind the flowers like wind. A signature beginning 'Gel...' appears on the right edge.</t>
+          <t>Pale pink four-petaled blossoms with yellow centers drift across a deep blue-violet background with pink and turquoise bands near the top. Thin white curved lines trail behind the flowers like wind.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -16816,7 +16816,7 @@
       <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>A night scene of many small white birds with red breasts perched on thin white lines like wires or branches against a black textured sky. A larger white bird flies near the top beside a small moon, and a large pale bird shape rests near the bottom center. The image is framed by a violet-blue painted border; the photo is slightly blurred.</t>
+          <t>A night scene of many small white birds with red breasts perched on thin white lines like wires or branches against a black textured sky. A larger white bird flies near the top beside a small moon, and a large pale bird shape rests near the bottom center. The image is framed by a violet-blue painted border.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -16916,7 +16916,7 @@
       <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>An all-over pattern of gold leaf-like shapes with fine orange veins, small dark dots and short turquoise brushstrokes on a reddish ground. The shapes swirl in many directions. Part of a gold frame is visible on the right.</t>
+          <t>An all-over pattern of gold leaf-like shapes with fine orange veins, small dark dots and short turquoise brushstrokes on a reddish ground. The shapes swirl in many directions.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -17016,7 +17016,7 @@
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>A dense abstract field of diagonal streaks in red, pink, green and purple, covered with small pink and turquoise dots. The strokes radiate as if from a burst. The photo is slightly blurred and has a light reflection on the right.</t>
+          <t>A dense abstract field of diagonal streaks in red, pink, green and purple, covered with small pink and turquoise dots. The strokes radiate as if from a burst.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>no depicted light source; glare on right</t>
+          <t>no depicted light source</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>An abstract of pinkish-violet hatched diagonal stripes forming zigzag bands, with wavy blue and red lines at the top. Small round yellow and green circles with dark centers, like eyes or seeds, are scattered across. A signature is in the lower right and part of a gold frame shows at the bottom.</t>
+          <t>An abstract of pinkish-violet hatched diagonal stripes forming zigzag bands, with wavy blue and red lines at the top. Small round yellow and green circles with dark centers, like eyes or seeds, are scattered across.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -17828,7 +17828,7 @@
       <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>An abstract painting dominated by warm pink, rust and peach shapes resembling two rounded forms or figures, outlined by dark teal arcs. A glare of light reflects in the upper center. The background edges are muted brown.</t>
+          <t>An abstract painting dominated by warm pink, rust and peach shapes resembling two rounded forms or figures, outlined by dark teal arcs. The background edges are muted brown.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -17863,7 +17863,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>glare on surface, no depicted source</t>
+          <t>no depicted light source</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -17963,7 +17963,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>no depicted light source; glare on surface</t>
+          <t>no depicted light source</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>no depicted light source; glare on surface</t>
+          <t>no depicted light source</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>no depicted light source; glare in the center</t>
+          <t>no depicted light source</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>no depicted light source; glare on surface</t>
+          <t>no depicted light source</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -19380,7 +19380,7 @@
       <c r="F94" s="2" t="n"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>A doll-like child figure with a pale face, large golden wig and gold puffed costume rides a rearing white horse with a red saddle and bridle against a dark green background. A golden feathered hat floats above the head, and golden clouds drift in the sky. Initials 'O.T.' appear in the lower right.</t>
+          <t>A doll-like child figure with a pale face, large golden wig and gold puffed costume rides a rearing white horse with a red saddle and bridle against a dark green background. A golden feathered hat floats above the head, and golden clouds drift in the sky.</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -19480,7 +19480,7 @@
       <c r="F95" s="2" t="n"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>A doll-like child figure with a pale face and big golden wig, in a gold puffed costume, rides a white horse with golden harness against a bright red background. A golden feathered hat floats above and golden clouds drift around. Initials 'O.T.' appear in the lower right.</t>
+          <t>A doll-like child figure with a pale face and big golden wig, in a gold puffed costume, rides a white horse with golden harness against a bright red background. A golden feathered hat floats above and golden clouds drift around.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>A woman with a stylized pale face, one large blue eye and a hand raised to her lips, wears a richly colored dress made of thick multicolored dabs. A small green hat sits on her head and the background is muted grey-green. A signature appears in the lower right.</t>
+          <t>A woman with a stylized pale face, one large blue eye and a hand raised to her lips, wears a richly colored dress made of thick multicolored dabs. A small green hat sits on her head and the background is muted grey-green.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -21040,7 +21040,7 @@
       <c r="F110" s="2" t="n"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>A tall thin standing figure wrapped in a red cloak, with a dark head, large round earrings and a long staff, stands on a white background. Splatters and drips of red and yellow ochre paint cover the background. A signature is at the bottom.</t>
+          <t>A tall thin standing figure wrapped in a red cloak, with a dark head, large round earrings and a long staff, stands on a white background. Splatters and drips of red and yellow ochre paint cover the background.</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -21532,7 +21532,7 @@
       <c r="F115" s="2" t="n"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>A rural Southeast Asian scene with thatched houses on stilts, laundry hanging on a line, and tall trees and mountains under a grey sky. A woman carries two baskets on a shoulder pole across a pale dirt road. 'NOY 2015' and 'Vientiane, Laos' are written in the lower left.</t>
+          <t>A rural Southeast Asian scene with thatched houses on stilts, laundry hanging on a line, and tall trees and mountains under a grey sky. A woman carries two baskets on a shoulder pole across a pale dirt road. 'Vientiane, Laos' is written in the lower left.</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -22032,7 +22032,7 @@
       <c r="F120" s="2" t="n"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>A black-and-white African village scene with thatched round huts on both sides of a path leading to the shore. Two palm trees rise in the center and a boat with a sail and two people floats on the water. Birds fly in the sky and a few figures stand by the huts; a signature is in the lower left.</t>
+          <t>A black-and-white African village scene with thatched round huts on both sides of a path leading to the shore. Two palm trees rise in the center and a boat with a sail and two people floats on the water. Birds fly in the sky and a few figures stand by the huts.</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>A symmetrical mask-like face drawn in oil pastel with large oval eyes in rings of green, blue, pink and white, a long brown nose and an orange layered mouth. Purple, blue and orange shapes form the cheeks and ears. A border of short green and purple strokes surrounds the face; glare is visible on the glass.</t>
+          <t>A symmetrical mask-like face drawn in oil pastel with large oval eyes in rings of green, blue, pink and white, a long brown nose and an orange layered mouth. Purple, blue and orange shapes form the cheeks and ears. A border of short green and purple strokes surrounds the face.</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -23219,7 +23219,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>flat, with glare on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -23292,7 +23292,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>A symmetrical abstract face built from bold bands: a red central nose shape flanked by blue and purple stripes, brown and pink eyebrow shapes, and a small red mouth near the bottom. Pale yellow, grey and light blue areas fill the background. Reflections of windows show on the glass.</t>
+          <t>A symmetrical abstract face built from bold bands: a red central nose shape flanked by blue and purple stripes, brown and pink eyebrow shapes, and a small red mouth near the bottom. Pale yellow, grey and light blue areas fill the background.</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -23327,7 +23327,7 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>flat, with reflections on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
@@ -23500,7 +23500,7 @@
       <c r="F134" s="2" t="n"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>An abstract with two glowing yellow areas on the left and center, surrounded by dark maroon, grey and black strokes, with a bright blue stripe running down the middle. Ochre and orange appear at the right edge. The surface is glossy with a strong reflection at the bottom.</t>
+          <t>An abstract with two glowing yellow areas on the left and center, surrounded by dark maroon, grey and black strokes, with a bright blue stripe running down the middle. Ochre and orange appear at the right edge. The surface is glossy.</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>no depicted light source; glare on surface</t>
+          <t>no depicted light source</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
@@ -24012,7 +24012,7 @@
       <c r="F139" s="2" t="n"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>A bold portrait of a bearded man with large dark eyes, a curling moustache and red lips, wearing a yellow and blue plumed hat and a red and white ruffled collar. The face is grey with heavy black brushstrokes. A date '5.6.4.69' and a signature are written at the top right.</t>
+          <t>A bold portrait of a bearded man with large dark eyes, a curling moustache and red lips, wearing a yellow and blue plumed hat and a red and white ruffled collar. The face is grey with heavy black brushstrokes.</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -24112,7 +24112,7 @@
       <c r="F140" s="2" t="n"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>A portrait of a bearded man with a plumed purple hat, red hair or collar and one large eye, his face split into light and dark halves. His blue doublet has fern-like patterns with orange circles. The background is beige cardboard-like with a white patch on the right; a number and signature appear at the top and bottom.</t>
+          <t>A portrait of a bearded man with a plumed purple hat, red hair or collar and one large eye, his face split into light and dark halves. His blue doublet has fern-like patterns with orange circles. The background is beige cardboard-like with a white patch on the right.</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>A white unicorn with a long flowing mane and a small flower on its horn stands on clouds. Thin leafy branches grow out of its back. The background is a sky-blue field sprinkled with gold specks and soft clouds; reflections on the glass are visible.</t>
+          <t>A white unicorn with a long flowing mane and a small flower on its horn stands on clouds. Thin leafy branches grow out of its back. The background is a sky-blue field sprinkled with gold specks and soft clouds.</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>A surreal flat composition with a grey airbrushed donkey standing on a pale green woven floor, its long braided tail curling up the left side. A dark bird flies at the top dropping pink blossoms, and grey stepped tower shapes and a colorful scale-patterned square stand behind. The background is white with a reflected window on the glass.</t>
+          <t>A surreal flat composition with a grey airbrushed donkey standing on a pale green woven floor, its long braided tail curling up the left side. A dark bird flies at the top dropping pink blossoms, and grey stepped tower shapes and a colorful scale-patterned square stand behind. The background is white.</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Two green tables with small colored balls on them stand on a yellow and orange floor, seen from above at a steep angle. The walls are teal and violet. The paint is thick and loosely applied.</t>
+          <t>Two green chairs with small colored balls on their seats stand on a yellow and orange floor, seen from above at a steep angle. The walls are teal and violet. The paint is thick and loosely applied.</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>tables, balls, floor, walls</t>
+          <t>chairs, balls, floor, walls</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -25344,7 +25344,7 @@
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>two tables on a diagonal in the lower half</t>
+          <t>two chairs on a diagonal in the lower half</t>
         </is>
       </c>
       <c r="P151" s="2" t="n"/>
@@ -25508,7 +25508,7 @@
       <c r="F153" s="2" t="n"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>An arched composition of a man with a moustache and cap playing an accordion beside a woman in a purple dotted dress holding a red flower. Behind them are a stone gateway, old houses with balconies, a church with a dome and a café sign reading 'ART CAFE', against a gold-leaf sky. A signature and '2021' appear at the bottom.</t>
+          <t>An arched composition of a man with a moustache and cap playing an accordion beside a woman in a purple dotted dress holding a red flower. Behind them are a stone gateway, old houses with balconies, a church with a dome and a café sign reading 'ART CAFE', against a gold-leaf sky.</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -26751,7 +26751,7 @@
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>flat, with glare on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
@@ -26951,7 +26951,7 @@
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>flat, with glare on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
@@ -27016,7 +27016,7 @@
       <c r="F168" s="2" t="n"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>A profile bust of an Egyptian queen with a tall flat-topped dark blue crown banded in red and gold, and a broad patterned collar. The figure is drawn with simple outlines on light papyrus. Strong reflections of a window and sky cover the glass.</t>
+          <t>A profile bust of an Egyptian queen with a tall flat-topped dark blue crown banded in red and gold, and a broad patterned collar. The figure is drawn with simple outlines on light papyrus.</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
-          <t>flat, with strong reflections on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O168" s="2" t="inlineStr">
@@ -27116,7 +27116,7 @@
       <c r="F169" s="2" t="n"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>An Egyptian-style papyrus scene of three female musicians: one plays a lute, one a long-necked instrument and one a harp, with a nude dancer-musician in the middle. Offering stands with vessels and grapes appear at the top. Strong reflections of windows cover the glass.</t>
+          <t>An Egyptian-style papyrus scene of three female musicians: one plays a lute, one a long-necked instrument and one a harp, with a nude dancer-musician in the middle. Offering stands with vessels and grapes appear at the top.</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>flat, with strong reflections on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
@@ -27216,7 +27216,7 @@
       <c r="F170" s="2" t="n"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>An Egyptian-style papyrus scene of two women walking hand in hand: a goddess with a horned sun-disc crown in a patterned purple and white dress holding a staff, and a queen in a tall feathered crown and pleated robe. Hieroglyphs and a cartouche are placed around them. Glare is visible on the glass.</t>
+          <t>An Egyptian-style papyrus scene of two women walking hand in hand: a goddess with a horned sun-disc crown in a patterned purple and white dress holding a staff, and a queen in a tall feathered crown and pleated robe. Hieroglyphs and a cartouche are placed around them.</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -27251,7 +27251,7 @@
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>flat, with glare on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O170" s="2" t="inlineStr">
@@ -27316,7 +27316,7 @@
       <c r="F171" s="2" t="n"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>An Egyptian-style papyrus profile bust of a queen wearing a vulture headdress and a broad red and gold collar, with long black hair. Hieroglyphs and a cartouche frame the head, and a band of lotus motifs runs along the bottom. Reflections of a window obscure part of the face.</t>
+          <t>An Egyptian-style papyrus profile bust of a queen wearing a vulture headdress and a broad red and gold collar, with long black hair. Hieroglyphs and a cartouche frame the head, and a band of lotus motifs runs along the bottom.</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -27351,7 +27351,7 @@
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>flat, with reflections on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
@@ -27951,7 +27951,7 @@
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>flat, with glare on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O177" s="2" t="inlineStr">
@@ -28051,7 +28051,7 @@
       </c>
       <c r="N178" s="2" t="inlineStr">
         <is>
-          <t>flat, with glare on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O178" s="2" t="inlineStr">
@@ -28628,7 +28628,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>A white house with small dark windows stands between two dark round trees under a deep blue night sky. The paint is extremely thick and crusty, built up in lumps. A signature and '2021' are in the lower left.</t>
+          <t>A white house with small dark windows stands between two dark round trees under a deep blue night sky. The paint is extremely thick and crusty, built up in lumps.</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -28724,7 +28724,7 @@
       <c r="F185" s="2" t="n"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>A densely packed hillside town of small houses with red, white and yellow walls, arched windows and red striped roofs, outlined in thick black lines. A winding yellow road cuts diagonally through the houses. The work is under glass with glare.</t>
+          <t>A densely packed hillside town of small houses with red, white and yellow walls, arched windows and red striped roofs, outlined in thick black lines. A winding yellow road cuts diagonally through the houses.</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -28759,7 +28759,7 @@
       </c>
       <c r="N185" s="2" t="inlineStr">
         <is>
-          <t>flat, with glare on glass</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="O185" s="2" t="inlineStr">
@@ -28824,7 +28824,7 @@
       <c r="F186" s="2" t="n"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>A bustling Central Asian street scene with figures in turbans and long robes walking and riding donkeys toward a large arched gateway. A blue-tiled dome rises behind yellow sunlit walls, and a man sits by the roadside on the left. A signature and '2016' appear in the lower left.</t>
+          <t>A bustling Central Asian street scene with figures in turbans and long robes walking and riding donkeys toward a large arched gateway. A blue-tiled dome rises behind yellow sunlit walls, and a man sits by the roadside on the left.</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -29324,7 +29324,7 @@
       <c r="F191" s="2" t="n"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>An abstracted market or riverside scene in palette-knife strokes, with figures in white conical hats carrying baskets on shoulder poles. Reds, greens, blues and blacks are set against a bright yellow ground. A signature appears in the lower left.</t>
+          <t>An abstracted market or riverside scene in palette-knife strokes, with figures in white conical hats carrying baskets on shoulder poles. Reds, greens, blues and blacks are set against a bright yellow ground.</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -29424,7 +29424,7 @@
       <c r="F192" s="2" t="n"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>An empty room seen in perspective with mustard-yellow walls and floor, and a window or painting opening onto a green landscape and blue sky at the back. Two dark figures embrace in the middle of the room, and two white dandelion-like circles sit on the floor. Yellow and dark paint is splattered across; a Georgian signature and '2019' appear at the lower right.</t>
+          <t>An empty room seen in perspective with mustard-yellow walls and floor, and a window or painting opening onto a green landscape and blue sky at the back. Two dark figures embrace in the middle of the room, and two white dandelion-like circles sit on the floor. Yellow and dark paint is splattered across.</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -29439,7 +29439,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>room, window, landscape, figures, dandelions, signature</t>
+          <t>room, window, landscape, figures, dandelions</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
